--- a/Shablon/MSO-X3104T.xlsx
+++ b/Shablon/MSO-X3104T.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="199">
   <si>
     <t>Параметр</t>
   </si>
@@ -399,21 +399,6 @@
   </si>
   <si>
     <t>Размах сигнала на частоте 1 ГГц, мВ</t>
-  </si>
-  <si>
-    <t>АО "Гос МКБ "Вымпел" им. И.И. Торопова"</t>
-  </si>
-  <si>
-    <t>СГМетр, лаборатория средств электрических и радиотехнических измерений</t>
-  </si>
-  <si>
-    <t>125424, г.Москва, Волоколамское шоссе, дом 90, стр. 23</t>
-  </si>
-  <si>
-    <t>Уникальный номер об аккредитации в реестре акредитованных лиц № РОСС СОБ 3.00231.2014</t>
-  </si>
-  <si>
-    <t>Тел.+7 (495) 491-05-31, 22-68, e-mail: ogmetr@vympelmkb.com</t>
   </si>
   <si>
     <t>Заключение:</t>
@@ -1124,62 +1109,155 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1188,124 +1266,31 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1620,74 +1605,64 @@
   <dimension ref="A1:I152"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="9" width="10.28515625" style="83" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="83"/>
+    <col min="1" max="9" width="10.28515625" style="34" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="34"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="82" t="s">
-        <v>120</v>
-      </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
+      <c r="A1" s="78"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="82" t="s">
-        <v>121</v>
-      </c>
-      <c r="B2" s="82"/>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="82"/>
-      <c r="I2" s="82"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="3" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="82" t="s">
-        <v>122</v>
-      </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
+      <c r="A3" s="78"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
     </row>
     <row r="4" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="84" t="s">
-        <v>123</v>
-      </c>
-      <c r="B4" s="84"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="84"/>
+      <c r="A4" s="79"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="79"/>
     </row>
     <row r="5" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="84" t="s">
-        <v>124</v>
-      </c>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
+      <c r="A5" s="79"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
     </row>
     <row r="6" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3"/>
@@ -1701,18 +1676,18 @@
       <c r="I6" s="3"/>
     </row>
     <row r="7" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="52" t="str">
+      <c r="A7" s="80" t="str">
         <f>"Протокол поверки № 10/"&amp;C139&amp;"/"&amp;D10</f>
         <v>Протокол поверки № 10/_date/_numb</v>
       </c>
-      <c r="B7" s="52"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
+      <c r="B7" s="80"/>
+      <c r="C7" s="80"/>
+      <c r="D7" s="80"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="80"/>
+      <c r="I7" s="80"/>
     </row>
     <row r="8" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="14"/>
@@ -1726,29 +1701,29 @@
       <c r="I8" s="14"/>
     </row>
     <row r="9" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="54" t="s">
+      <c r="A9" s="87" t="s">
         <v>87</v>
       </c>
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
+      <c r="B9" s="87"/>
+      <c r="C9" s="87"/>
       <c r="D9" s="16" t="s">
         <v>88</v>
       </c>
       <c r="E9" s="17"/>
-      <c r="F9" s="85" t="s">
+      <c r="F9" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="G9" s="86"/>
+      <c r="G9" s="36"/>
       <c r="H9" s="17"/>
       <c r="I9" s="22"/>
     </row>
     <row r="10" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="54" t="s">
+      <c r="A10" s="87" t="s">
         <v>90</v>
       </c>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="87" t="s">
+      <c r="B10" s="87"/>
+      <c r="C10" s="87"/>
+      <c r="D10" s="37" t="s">
         <v>91</v>
       </c>
       <c r="E10" s="17"/>
@@ -1758,11 +1733,11 @@
       <c r="I10" s="22"/>
     </row>
     <row r="11" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="54" t="s">
+      <c r="A11" s="87" t="s">
         <v>92</v>
       </c>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
+      <c r="B11" s="87"/>
+      <c r="C11" s="87"/>
       <c r="D11" s="16"/>
       <c r="E11" s="17"/>
       <c r="F11" s="17"/>
@@ -1771,11 +1746,11 @@
       <c r="I11" s="22"/>
     </row>
     <row r="12" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="54" t="s">
+      <c r="A12" s="87" t="s">
         <v>93</v>
       </c>
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
+      <c r="B12" s="87"/>
+      <c r="C12" s="87"/>
       <c r="D12" s="18" t="s">
         <v>107</v>
       </c>
@@ -1786,12 +1761,12 @@
       <c r="I12" s="22"/>
     </row>
     <row r="13" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="54" t="s">
+      <c r="A13" s="87" t="s">
         <v>94</v>
       </c>
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="87" t="s">
+      <c r="B13" s="87"/>
+      <c r="C13" s="87"/>
+      <c r="D13" s="37" t="s">
         <v>95</v>
       </c>
       <c r="E13" s="17"/>
@@ -1801,11 +1776,11 @@
       <c r="I13" s="22"/>
     </row>
     <row r="14" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="54" t="s">
+      <c r="A14" s="87" t="s">
         <v>96</v>
       </c>
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
+      <c r="B14" s="87"/>
+      <c r="C14" s="87"/>
       <c r="D14" s="16" t="s">
         <v>98</v>
       </c>
@@ -1816,11 +1791,11 @@
       <c r="I14" s="22"/>
     </row>
     <row r="15" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="54" t="s">
-        <v>192</v>
-      </c>
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
+      <c r="A15" s="87" t="s">
+        <v>187</v>
+      </c>
+      <c r="B15" s="87"/>
+      <c r="C15" s="87"/>
       <c r="D15" s="16" t="s">
         <v>97</v>
       </c>
@@ -1853,28 +1828,28 @@
       <c r="I17" s="32"/>
     </row>
     <row r="18" spans="1:9" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="41" t="s">
+      <c r="A18" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="41"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
+      <c r="B18" s="89"/>
+      <c r="C18" s="89"/>
+      <c r="D18" s="89"/>
     </row>
     <row r="19" spans="1:9" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="42" t="s">
+      <c r="A19" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="B19" s="42"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="36" t="s">
+      <c r="B19" s="90"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="90"/>
+      <c r="E19" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36" t="s">
+      <c r="F19" s="72"/>
+      <c r="G19" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="H19" s="36"/>
+      <c r="H19" s="72"/>
     </row>
     <row r="20" spans="1:9" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
@@ -1883,74 +1858,74 @@
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
       <c r="D20" s="13"/>
-      <c r="E20" s="88" t="s">
+      <c r="E20" s="91" t="s">
         <v>99</v>
       </c>
-      <c r="F20" s="89"/>
-      <c r="G20" s="43" t="s">
+      <c r="F20" s="84"/>
+      <c r="G20" s="85" t="s">
         <v>3</v>
       </c>
-      <c r="H20" s="43"/>
+      <c r="H20" s="85"/>
     </row>
     <row r="21" spans="1:9" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="44" t="s">
+      <c r="A21" s="92" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="45"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="46"/>
-      <c r="E21" s="89" t="s">
+      <c r="B21" s="93"/>
+      <c r="C21" s="93"/>
+      <c r="D21" s="94"/>
+      <c r="E21" s="84" t="s">
         <v>100</v>
       </c>
-      <c r="F21" s="89"/>
-      <c r="G21" s="43" t="s">
+      <c r="F21" s="84"/>
+      <c r="G21" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="H21" s="43"/>
+      <c r="H21" s="85"/>
     </row>
     <row r="22" spans="1:9" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="47" t="s">
+      <c r="A22" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="B22" s="48"/>
-      <c r="C22" s="48"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="89" t="s">
+      <c r="B22" s="82"/>
+      <c r="C22" s="82"/>
+      <c r="D22" s="83"/>
+      <c r="E22" s="84" t="s">
         <v>101</v>
       </c>
-      <c r="F22" s="89"/>
-      <c r="G22" s="43" t="s">
+      <c r="F22" s="84"/>
+      <c r="G22" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="H22" s="43"/>
+      <c r="H22" s="85"/>
     </row>
     <row r="23" spans="1:9" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="47" t="s">
+      <c r="A23" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="B23" s="48"/>
-      <c r="C23" s="48"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="89"/>
-      <c r="F23" s="89"/>
-      <c r="G23" s="43" t="s">
+      <c r="B23" s="82"/>
+      <c r="C23" s="82"/>
+      <c r="D23" s="83"/>
+      <c r="E23" s="84"/>
+      <c r="F23" s="84"/>
+      <c r="G23" s="85" t="s">
         <v>12</v>
       </c>
-      <c r="H23" s="43"/>
+      <c r="H23" s="85"/>
     </row>
     <row r="24" spans="1:9" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="47" t="s">
+      <c r="A24" s="81" t="s">
         <v>7</v>
       </c>
-      <c r="B24" s="48"/>
-      <c r="C24" s="48"/>
-      <c r="D24" s="49"/>
-      <c r="E24" s="89"/>
-      <c r="F24" s="89"/>
-      <c r="G24" s="43" t="s">
+      <c r="B24" s="82"/>
+      <c r="C24" s="82"/>
+      <c r="D24" s="83"/>
+      <c r="E24" s="84"/>
+      <c r="F24" s="84"/>
+      <c r="G24" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="H24" s="43"/>
+      <c r="H24" s="85"/>
     </row>
     <row r="25" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
@@ -1965,7 +1940,7 @@
     </row>
     <row r="26" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="26" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -1989,7 +1964,7 @@
     </row>
     <row r="28" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="32" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B28" s="32"/>
       <c r="C28" s="5"/>
@@ -2002,7 +1977,7 @@
     </row>
     <row r="29" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="32" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B29" s="32"/>
       <c r="C29" s="32"/>
@@ -2014,17 +1989,17 @@
       <c r="I29" s="4"/>
     </row>
     <row r="30" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="53" t="s">
-        <v>196</v>
-      </c>
-      <c r="B30" s="53"/>
-      <c r="C30" s="53"/>
-      <c r="D30" s="53"/>
-      <c r="E30" s="53"/>
-      <c r="F30" s="53"/>
-      <c r="G30" s="53"/>
-      <c r="H30" s="53"/>
-      <c r="I30" s="53"/>
+      <c r="A30" s="86" t="s">
+        <v>191</v>
+      </c>
+      <c r="B30" s="86"/>
+      <c r="C30" s="86"/>
+      <c r="D30" s="86"/>
+      <c r="E30" s="86"/>
+      <c r="F30" s="86"/>
+      <c r="G30" s="86"/>
+      <c r="H30" s="86"/>
+      <c r="I30" s="86"/>
     </row>
     <row r="31" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
@@ -2041,7 +2016,7 @@
     </row>
     <row r="32" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -2066,299 +2041,299 @@
       <c r="I33" s="4"/>
     </row>
     <row r="34" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="55" t="s">
+      <c r="A34" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="B34" s="56"/>
-      <c r="C34" s="55" t="s">
+      <c r="B34" s="46"/>
+      <c r="C34" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="D34" s="56"/>
-      <c r="E34" s="67" t="s">
+      <c r="D34" s="46"/>
+      <c r="E34" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="F34" s="55" t="s">
+      <c r="F34" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="G34" s="56"/>
-      <c r="H34" s="61" t="s">
+      <c r="G34" s="46"/>
+      <c r="H34" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="I34" s="62"/>
+      <c r="I34" s="60"/>
     </row>
     <row r="35" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="57"/>
       <c r="B35" s="58"/>
       <c r="C35" s="57"/>
       <c r="D35" s="58"/>
-      <c r="E35" s="68"/>
+      <c r="E35" s="56"/>
       <c r="F35" s="57"/>
       <c r="G35" s="58"/>
-      <c r="H35" s="63"/>
-      <c r="I35" s="64"/>
+      <c r="H35" s="61"/>
+      <c r="I35" s="62"/>
     </row>
     <row r="36" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="59"/>
-      <c r="B36" s="60"/>
-      <c r="C36" s="59"/>
-      <c r="D36" s="60"/>
-      <c r="E36" s="69"/>
-      <c r="F36" s="59"/>
-      <c r="G36" s="60"/>
-      <c r="H36" s="65"/>
-      <c r="I36" s="66"/>
+      <c r="A36" s="47"/>
+      <c r="B36" s="48"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="48"/>
+      <c r="H36" s="63"/>
+      <c r="I36" s="64"/>
     </row>
     <row r="37" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="34" t="s">
+      <c r="A37" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="B37" s="34"/>
-      <c r="C37" s="34" t="s">
+      <c r="B37" s="65"/>
+      <c r="C37" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="D37" s="34"/>
-      <c r="E37" s="90" t="s">
+      <c r="D37" s="65"/>
+      <c r="E37" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="F37" s="65" t="s">
+        <v>40</v>
+      </c>
+      <c r="G37" s="65"/>
+      <c r="H37" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="I37" s="66"/>
+    </row>
+    <row r="38" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="65" t="s">
+        <v>19</v>
+      </c>
+      <c r="B38" s="65"/>
+      <c r="C38" s="77" t="s">
+        <v>30</v>
+      </c>
+      <c r="D38" s="77"/>
+      <c r="E38" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="F38" s="65" t="s">
+        <v>41</v>
+      </c>
+      <c r="G38" s="65"/>
+      <c r="H38" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="I38" s="66"/>
+    </row>
+    <row r="39" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="65" t="s">
+        <v>20</v>
+      </c>
+      <c r="B39" s="65"/>
+      <c r="C39" s="65" t="s">
+        <v>31</v>
+      </c>
+      <c r="D39" s="65"/>
+      <c r="E39" s="38" t="s">
+        <v>125</v>
+      </c>
+      <c r="F39" s="65" t="s">
+        <v>42</v>
+      </c>
+      <c r="G39" s="65"/>
+      <c r="H39" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="I39" s="65"/>
+    </row>
+    <row r="40" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="65" t="s">
+        <v>21</v>
+      </c>
+      <c r="B40" s="65"/>
+      <c r="C40" s="65" t="s">
+        <v>32</v>
+      </c>
+      <c r="D40" s="65"/>
+      <c r="E40" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="F40" s="65" t="s">
+        <v>43</v>
+      </c>
+      <c r="G40" s="65"/>
+      <c r="H40" s="65" t="s">
+        <v>54</v>
+      </c>
+      <c r="I40" s="65"/>
+    </row>
+    <row r="41" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="B41" s="65"/>
+      <c r="C41" s="77" t="s">
+        <v>33</v>
+      </c>
+      <c r="D41" s="77"/>
+      <c r="E41" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="F41" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="G41" s="65"/>
+      <c r="H41" s="65" t="s">
+        <v>55</v>
+      </c>
+      <c r="I41" s="65"/>
+    </row>
+    <row r="42" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="65" t="s">
+        <v>23</v>
+      </c>
+      <c r="B42" s="65"/>
+      <c r="C42" s="65" t="s">
+        <v>34</v>
+      </c>
+      <c r="D42" s="65"/>
+      <c r="E42" s="38" t="s">
         <v>128</v>
       </c>
-      <c r="F37" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="G37" s="34"/>
-      <c r="H37" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="I37" s="38"/>
-    </row>
-    <row r="38" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="B38" s="34"/>
-      <c r="C38" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="D38" s="39"/>
-      <c r="E38" s="90" t="s">
+      <c r="F42" s="65" t="s">
+        <v>45</v>
+      </c>
+      <c r="G42" s="65"/>
+      <c r="H42" s="65" t="s">
+        <v>56</v>
+      </c>
+      <c r="I42" s="65"/>
+    </row>
+    <row r="43" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="B43" s="65"/>
+      <c r="C43" s="65" t="s">
+        <v>35</v>
+      </c>
+      <c r="D43" s="65"/>
+      <c r="E43" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="F38" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="G38" s="34"/>
-      <c r="H38" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="I38" s="38"/>
-    </row>
-    <row r="39" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="B39" s="34"/>
-      <c r="C39" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="D39" s="34"/>
-      <c r="E39" s="90" t="s">
+      <c r="F43" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65" t="s">
+        <v>57</v>
+      </c>
+      <c r="I43" s="65"/>
+    </row>
+    <row r="44" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44" s="65"/>
+      <c r="C44" s="65" t="s">
+        <v>36</v>
+      </c>
+      <c r="D44" s="65"/>
+      <c r="E44" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="F39" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="G39" s="34"/>
-      <c r="H39" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="I39" s="34"/>
-    </row>
-    <row r="40" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="B40" s="34"/>
-      <c r="C40" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="D40" s="34"/>
-      <c r="E40" s="90" t="s">
+      <c r="F44" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="G44" s="65"/>
+      <c r="H44" s="65" t="s">
+        <v>58</v>
+      </c>
+      <c r="I44" s="65"/>
+    </row>
+    <row r="45" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="65" t="s">
+        <v>26</v>
+      </c>
+      <c r="B45" s="65"/>
+      <c r="C45" s="65" t="s">
+        <v>37</v>
+      </c>
+      <c r="D45" s="65"/>
+      <c r="E45" s="38" t="s">
         <v>131</v>
       </c>
-      <c r="F40" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="G40" s="34"/>
-      <c r="H40" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="I40" s="34"/>
-    </row>
-    <row r="41" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="B41" s="34"/>
-      <c r="C41" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="D41" s="39"/>
-      <c r="E41" s="90" t="s">
+      <c r="F45" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="G45" s="65"/>
+      <c r="H45" s="66" t="s">
+        <v>59</v>
+      </c>
+      <c r="I45" s="66"/>
+    </row>
+    <row r="46" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="65" t="s">
+        <v>27</v>
+      </c>
+      <c r="B46" s="65"/>
+      <c r="C46" s="65" t="s">
+        <v>38</v>
+      </c>
+      <c r="D46" s="65"/>
+      <c r="E46" s="38" t="s">
         <v>132</v>
       </c>
-      <c r="F41" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="G41" s="34"/>
-      <c r="H41" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="I41" s="34"/>
-    </row>
-    <row r="42" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="B42" s="34"/>
-      <c r="C42" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D42" s="34"/>
-      <c r="E42" s="90" t="s">
+      <c r="F46" s="77" t="s">
+        <v>49</v>
+      </c>
+      <c r="G46" s="77"/>
+      <c r="H46" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="I46" s="77"/>
+    </row>
+    <row r="47" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="65" t="s">
+        <v>28</v>
+      </c>
+      <c r="B47" s="65"/>
+      <c r="C47" s="65" t="s">
+        <v>39</v>
+      </c>
+      <c r="D47" s="65"/>
+      <c r="E47" s="38" t="s">
         <v>133</v>
       </c>
-      <c r="F42" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="G42" s="34"/>
-      <c r="H42" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="I42" s="34"/>
-    </row>
-    <row r="43" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="B43" s="34"/>
-      <c r="C43" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="D43" s="34"/>
-      <c r="E43" s="90" t="s">
+      <c r="F47" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="G47" s="65"/>
+      <c r="H47" s="66" t="s">
+        <v>61</v>
+      </c>
+      <c r="I47" s="66"/>
+    </row>
+    <row r="48" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="65" t="s">
+        <v>108</v>
+      </c>
+      <c r="B48" s="65"/>
+      <c r="C48" s="65" t="s">
+        <v>109</v>
+      </c>
+      <c r="D48" s="65"/>
+      <c r="E48" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="F43" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="G43" s="34"/>
-      <c r="H43" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="I43" s="34"/>
-    </row>
-    <row r="44" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="B44" s="34"/>
-      <c r="C44" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="D44" s="34"/>
-      <c r="E44" s="90" t="s">
-        <v>135</v>
-      </c>
-      <c r="F44" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="G44" s="34"/>
-      <c r="H44" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="I44" s="34"/>
-    </row>
-    <row r="45" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="B45" s="34"/>
-      <c r="C45" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="D45" s="34"/>
-      <c r="E45" s="90" t="s">
-        <v>136</v>
-      </c>
-      <c r="F45" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="G45" s="34"/>
-      <c r="H45" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="I45" s="38"/>
-    </row>
-    <row r="46" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="B46" s="34"/>
-      <c r="C46" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="D46" s="34"/>
-      <c r="E46" s="90" t="s">
-        <v>137</v>
-      </c>
-      <c r="F46" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="G46" s="39"/>
-      <c r="H46" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="I46" s="39"/>
-    </row>
-    <row r="47" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="B47" s="34"/>
-      <c r="C47" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="D47" s="34"/>
-      <c r="E47" s="90" t="s">
-        <v>138</v>
-      </c>
-      <c r="F47" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="G47" s="34"/>
-      <c r="H47" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="I47" s="38"/>
-    </row>
-    <row r="48" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="B48" s="34"/>
-      <c r="C48" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="D48" s="34"/>
-      <c r="E48" s="90" t="s">
-        <v>139</v>
-      </c>
-      <c r="F48" s="34" t="s">
+      <c r="F48" s="65" t="s">
         <v>110</v>
       </c>
-      <c r="G48" s="34"/>
-      <c r="H48" s="38" t="s">
+      <c r="G48" s="65"/>
+      <c r="H48" s="66" t="s">
         <v>111</v>
       </c>
-      <c r="I48" s="38"/>
+      <c r="I48" s="66"/>
     </row>
     <row r="49" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
@@ -2374,299 +2349,299 @@
       <c r="I49" s="4"/>
     </row>
     <row r="50" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="55" t="s">
+      <c r="A50" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="B50" s="56"/>
-      <c r="C50" s="55" t="s">
+      <c r="B50" s="46"/>
+      <c r="C50" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="D50" s="56"/>
-      <c r="E50" s="67" t="s">
+      <c r="D50" s="46"/>
+      <c r="E50" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="F50" s="55" t="s">
+      <c r="F50" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="G50" s="56"/>
-      <c r="H50" s="61" t="s">
+      <c r="G50" s="46"/>
+      <c r="H50" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="I50" s="62"/>
+      <c r="I50" s="60"/>
     </row>
     <row r="51" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="57"/>
       <c r="B51" s="58"/>
       <c r="C51" s="57"/>
       <c r="D51" s="58"/>
-      <c r="E51" s="68"/>
+      <c r="E51" s="56"/>
       <c r="F51" s="57"/>
       <c r="G51" s="58"/>
-      <c r="H51" s="63"/>
-      <c r="I51" s="64"/>
+      <c r="H51" s="61"/>
+      <c r="I51" s="62"/>
     </row>
     <row r="52" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="59"/>
-      <c r="B52" s="60"/>
-      <c r="C52" s="59"/>
-      <c r="D52" s="60"/>
-      <c r="E52" s="69"/>
-      <c r="F52" s="59"/>
-      <c r="G52" s="60"/>
-      <c r="H52" s="65"/>
-      <c r="I52" s="66"/>
+      <c r="A52" s="47"/>
+      <c r="B52" s="48"/>
+      <c r="C52" s="47"/>
+      <c r="D52" s="48"/>
+      <c r="E52" s="53"/>
+      <c r="F52" s="47"/>
+      <c r="G52" s="48"/>
+      <c r="H52" s="63"/>
+      <c r="I52" s="64"/>
     </row>
     <row r="53" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="34" t="s">
+      <c r="A53" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="B53" s="34"/>
-      <c r="C53" s="34" t="s">
+      <c r="B53" s="65"/>
+      <c r="C53" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="D53" s="34"/>
-      <c r="E53" s="90" t="s">
+      <c r="D53" s="65"/>
+      <c r="E53" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="F53" s="65" t="s">
+        <v>40</v>
+      </c>
+      <c r="G53" s="65"/>
+      <c r="H53" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="I53" s="66"/>
+    </row>
+    <row r="54" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="65" t="s">
+        <v>19</v>
+      </c>
+      <c r="B54" s="65"/>
+      <c r="C54" s="77" t="s">
+        <v>30</v>
+      </c>
+      <c r="D54" s="77"/>
+      <c r="E54" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="F54" s="65" t="s">
+        <v>41</v>
+      </c>
+      <c r="G54" s="65"/>
+      <c r="H54" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="I54" s="66"/>
+    </row>
+    <row r="55" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="65" t="s">
+        <v>20</v>
+      </c>
+      <c r="B55" s="65"/>
+      <c r="C55" s="65" t="s">
+        <v>31</v>
+      </c>
+      <c r="D55" s="65"/>
+      <c r="E55" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="F55" s="65" t="s">
+        <v>42</v>
+      </c>
+      <c r="G55" s="65"/>
+      <c r="H55" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="I55" s="65"/>
+    </row>
+    <row r="56" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="65" t="s">
+        <v>21</v>
+      </c>
+      <c r="B56" s="65"/>
+      <c r="C56" s="65" t="s">
+        <v>32</v>
+      </c>
+      <c r="D56" s="65"/>
+      <c r="E56" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="F56" s="65" t="s">
+        <v>43</v>
+      </c>
+      <c r="G56" s="65"/>
+      <c r="H56" s="65" t="s">
+        <v>54</v>
+      </c>
+      <c r="I56" s="65"/>
+    </row>
+    <row r="57" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="B57" s="65"/>
+      <c r="C57" s="77" t="s">
+        <v>33</v>
+      </c>
+      <c r="D57" s="77"/>
+      <c r="E57" s="38" t="s">
+        <v>139</v>
+      </c>
+      <c r="F57" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="G57" s="65"/>
+      <c r="H57" s="65" t="s">
+        <v>55</v>
+      </c>
+      <c r="I57" s="65"/>
+    </row>
+    <row r="58" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="65" t="s">
+        <v>23</v>
+      </c>
+      <c r="B58" s="65"/>
+      <c r="C58" s="65" t="s">
+        <v>34</v>
+      </c>
+      <c r="D58" s="65"/>
+      <c r="E58" s="38" t="s">
         <v>140</v>
       </c>
-      <c r="F53" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="G53" s="34"/>
-      <c r="H53" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="I53" s="38"/>
-    </row>
-    <row r="54" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="B54" s="34"/>
-      <c r="C54" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="D54" s="39"/>
-      <c r="E54" s="90" t="s">
+      <c r="F58" s="65" t="s">
+        <v>45</v>
+      </c>
+      <c r="G58" s="65"/>
+      <c r="H58" s="65" t="s">
+        <v>56</v>
+      </c>
+      <c r="I58" s="65"/>
+    </row>
+    <row r="59" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="B59" s="65"/>
+      <c r="C59" s="65" t="s">
+        <v>35</v>
+      </c>
+      <c r="D59" s="65"/>
+      <c r="E59" s="38" t="s">
         <v>141</v>
       </c>
-      <c r="F54" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="G54" s="34"/>
-      <c r="H54" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="I54" s="38"/>
-    </row>
-    <row r="55" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="B55" s="34"/>
-      <c r="C55" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="D55" s="34"/>
-      <c r="E55" s="90" t="s">
+      <c r="F59" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="G59" s="65"/>
+      <c r="H59" s="65" t="s">
+        <v>57</v>
+      </c>
+      <c r="I59" s="65"/>
+    </row>
+    <row r="60" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="B60" s="65"/>
+      <c r="C60" s="65" t="s">
+        <v>36</v>
+      </c>
+      <c r="D60" s="65"/>
+      <c r="E60" s="38" t="s">
         <v>142</v>
       </c>
-      <c r="F55" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="G55" s="34"/>
-      <c r="H55" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="I55" s="34"/>
-    </row>
-    <row r="56" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="B56" s="34"/>
-      <c r="C56" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="D56" s="34"/>
-      <c r="E56" s="90" t="s">
+      <c r="F60" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="G60" s="65"/>
+      <c r="H60" s="65" t="s">
+        <v>58</v>
+      </c>
+      <c r="I60" s="65"/>
+    </row>
+    <row r="61" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="65" t="s">
+        <v>26</v>
+      </c>
+      <c r="B61" s="65"/>
+      <c r="C61" s="65" t="s">
+        <v>37</v>
+      </c>
+      <c r="D61" s="65"/>
+      <c r="E61" s="38" t="s">
         <v>143</v>
       </c>
-      <c r="F56" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="G56" s="34"/>
-      <c r="H56" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="I56" s="34"/>
-    </row>
-    <row r="57" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="B57" s="34"/>
-      <c r="C57" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="D57" s="39"/>
-      <c r="E57" s="90" t="s">
+      <c r="F61" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="G61" s="65"/>
+      <c r="H61" s="66" t="s">
+        <v>59</v>
+      </c>
+      <c r="I61" s="66"/>
+    </row>
+    <row r="62" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="65" t="s">
+        <v>27</v>
+      </c>
+      <c r="B62" s="65"/>
+      <c r="C62" s="65" t="s">
+        <v>38</v>
+      </c>
+      <c r="D62" s="65"/>
+      <c r="E62" s="38" t="s">
         <v>144</v>
       </c>
-      <c r="F57" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="G57" s="34"/>
-      <c r="H57" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="I57" s="34"/>
-    </row>
-    <row r="58" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="B58" s="34"/>
-      <c r="C58" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D58" s="34"/>
-      <c r="E58" s="90" t="s">
+      <c r="F62" s="77" t="s">
+        <v>49</v>
+      </c>
+      <c r="G62" s="77"/>
+      <c r="H62" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="I62" s="77"/>
+    </row>
+    <row r="63" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="65" t="s">
+        <v>28</v>
+      </c>
+      <c r="B63" s="65"/>
+      <c r="C63" s="65" t="s">
+        <v>39</v>
+      </c>
+      <c r="D63" s="65"/>
+      <c r="E63" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="F58" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="G58" s="34"/>
-      <c r="H58" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="I58" s="34"/>
-    </row>
-    <row r="59" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="B59" s="34"/>
-      <c r="C59" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="D59" s="34"/>
-      <c r="E59" s="90" t="s">
+      <c r="F63" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="G63" s="65"/>
+      <c r="H63" s="66" t="s">
+        <v>61</v>
+      </c>
+      <c r="I63" s="66"/>
+    </row>
+    <row r="64" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="65" t="s">
+        <v>108</v>
+      </c>
+      <c r="B64" s="65"/>
+      <c r="C64" s="65" t="s">
+        <v>109</v>
+      </c>
+      <c r="D64" s="65"/>
+      <c r="E64" s="38" t="s">
         <v>146</v>
       </c>
-      <c r="F59" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="G59" s="34"/>
-      <c r="H59" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="I59" s="34"/>
-    </row>
-    <row r="60" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="B60" s="34"/>
-      <c r="C60" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="D60" s="34"/>
-      <c r="E60" s="90" t="s">
-        <v>147</v>
-      </c>
-      <c r="F60" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="G60" s="34"/>
-      <c r="H60" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="I60" s="34"/>
-    </row>
-    <row r="61" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="B61" s="34"/>
-      <c r="C61" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="D61" s="34"/>
-      <c r="E61" s="90" t="s">
-        <v>148</v>
-      </c>
-      <c r="F61" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="G61" s="34"/>
-      <c r="H61" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="I61" s="38"/>
-    </row>
-    <row r="62" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="B62" s="34"/>
-      <c r="C62" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="D62" s="34"/>
-      <c r="E62" s="90" t="s">
-        <v>149</v>
-      </c>
-      <c r="F62" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="G62" s="39"/>
-      <c r="H62" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="I62" s="39"/>
-    </row>
-    <row r="63" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="B63" s="34"/>
-      <c r="C63" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="D63" s="34"/>
-      <c r="E63" s="90" t="s">
-        <v>150</v>
-      </c>
-      <c r="F63" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="G63" s="34"/>
-      <c r="H63" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="I63" s="38"/>
-    </row>
-    <row r="64" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="B64" s="34"/>
-      <c r="C64" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="D64" s="34"/>
-      <c r="E64" s="90" t="s">
-        <v>151</v>
-      </c>
-      <c r="F64" s="34" t="s">
+      <c r="F64" s="65" t="s">
         <v>110</v>
       </c>
-      <c r="G64" s="34"/>
-      <c r="H64" s="38" t="s">
+      <c r="G64" s="65"/>
+      <c r="H64" s="66" t="s">
         <v>111</v>
       </c>
-      <c r="I64" s="38"/>
+      <c r="I64" s="66"/>
     </row>
     <row r="65" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
@@ -2682,299 +2657,299 @@
       <c r="I65" s="4"/>
     </row>
     <row r="66" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="55" t="s">
+      <c r="A66" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="B66" s="56"/>
-      <c r="C66" s="55" t="s">
+      <c r="B66" s="46"/>
+      <c r="C66" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="D66" s="56"/>
-      <c r="E66" s="67" t="s">
+      <c r="D66" s="46"/>
+      <c r="E66" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="F66" s="55" t="s">
+      <c r="F66" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="G66" s="56"/>
-      <c r="H66" s="61" t="s">
+      <c r="G66" s="46"/>
+      <c r="H66" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="I66" s="62"/>
+      <c r="I66" s="60"/>
     </row>
     <row r="67" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="57"/>
       <c r="B67" s="58"/>
       <c r="C67" s="57"/>
       <c r="D67" s="58"/>
-      <c r="E67" s="68"/>
+      <c r="E67" s="56"/>
       <c r="F67" s="57"/>
       <c r="G67" s="58"/>
-      <c r="H67" s="63"/>
-      <c r="I67" s="64"/>
+      <c r="H67" s="61"/>
+      <c r="I67" s="62"/>
     </row>
     <row r="68" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="59"/>
-      <c r="B68" s="60"/>
-      <c r="C68" s="59"/>
-      <c r="D68" s="60"/>
-      <c r="E68" s="69"/>
-      <c r="F68" s="59"/>
-      <c r="G68" s="60"/>
-      <c r="H68" s="65"/>
-      <c r="I68" s="66"/>
+      <c r="A68" s="47"/>
+      <c r="B68" s="48"/>
+      <c r="C68" s="47"/>
+      <c r="D68" s="48"/>
+      <c r="E68" s="53"/>
+      <c r="F68" s="47"/>
+      <c r="G68" s="48"/>
+      <c r="H68" s="63"/>
+      <c r="I68" s="64"/>
     </row>
     <row r="69" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="34" t="s">
+      <c r="A69" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="B69" s="34"/>
-      <c r="C69" s="34" t="s">
+      <c r="B69" s="65"/>
+      <c r="C69" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="D69" s="34"/>
-      <c r="E69" s="90" t="s">
+      <c r="D69" s="65"/>
+      <c r="E69" s="38" t="s">
+        <v>147</v>
+      </c>
+      <c r="F69" s="65" t="s">
+        <v>40</v>
+      </c>
+      <c r="G69" s="65"/>
+      <c r="H69" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="I69" s="66"/>
+    </row>
+    <row r="70" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="65" t="s">
+        <v>19</v>
+      </c>
+      <c r="B70" s="65"/>
+      <c r="C70" s="77" t="s">
+        <v>30</v>
+      </c>
+      <c r="D70" s="77"/>
+      <c r="E70" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="F70" s="65" t="s">
+        <v>41</v>
+      </c>
+      <c r="G70" s="65"/>
+      <c r="H70" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="I70" s="66"/>
+    </row>
+    <row r="71" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="65" t="s">
+        <v>20</v>
+      </c>
+      <c r="B71" s="65"/>
+      <c r="C71" s="65" t="s">
+        <v>31</v>
+      </c>
+      <c r="D71" s="65"/>
+      <c r="E71" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="F71" s="65" t="s">
+        <v>42</v>
+      </c>
+      <c r="G71" s="65"/>
+      <c r="H71" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="I71" s="65"/>
+    </row>
+    <row r="72" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="65" t="s">
+        <v>21</v>
+      </c>
+      <c r="B72" s="65"/>
+      <c r="C72" s="65" t="s">
+        <v>32</v>
+      </c>
+      <c r="D72" s="65"/>
+      <c r="E72" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="F72" s="65" t="s">
+        <v>43</v>
+      </c>
+      <c r="G72" s="65"/>
+      <c r="H72" s="65" t="s">
+        <v>54</v>
+      </c>
+      <c r="I72" s="65"/>
+    </row>
+    <row r="73" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="B73" s="65"/>
+      <c r="C73" s="77" t="s">
+        <v>33</v>
+      </c>
+      <c r="D73" s="77"/>
+      <c r="E73" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="F73" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="G73" s="65"/>
+      <c r="H73" s="65" t="s">
+        <v>55</v>
+      </c>
+      <c r="I73" s="65"/>
+    </row>
+    <row r="74" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="65" t="s">
+        <v>23</v>
+      </c>
+      <c r="B74" s="65"/>
+      <c r="C74" s="65" t="s">
+        <v>34</v>
+      </c>
+      <c r="D74" s="65"/>
+      <c r="E74" s="38" t="s">
         <v>152</v>
       </c>
-      <c r="F69" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="G69" s="34"/>
-      <c r="H69" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="I69" s="38"/>
-    </row>
-    <row r="70" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="B70" s="34"/>
-      <c r="C70" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="D70" s="39"/>
-      <c r="E70" s="90" t="s">
+      <c r="F74" s="65" t="s">
+        <v>45</v>
+      </c>
+      <c r="G74" s="65"/>
+      <c r="H74" s="65" t="s">
+        <v>56</v>
+      </c>
+      <c r="I74" s="65"/>
+    </row>
+    <row r="75" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="B75" s="65"/>
+      <c r="C75" s="65" t="s">
+        <v>35</v>
+      </c>
+      <c r="D75" s="65"/>
+      <c r="E75" s="38" t="s">
         <v>153</v>
       </c>
-      <c r="F70" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="G70" s="34"/>
-      <c r="H70" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="I70" s="38"/>
-    </row>
-    <row r="71" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="B71" s="34"/>
-      <c r="C71" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="D71" s="34"/>
-      <c r="E71" s="90" t="s">
+      <c r="F75" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="G75" s="65"/>
+      <c r="H75" s="65" t="s">
+        <v>57</v>
+      </c>
+      <c r="I75" s="65"/>
+    </row>
+    <row r="76" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="B76" s="65"/>
+      <c r="C76" s="65" t="s">
+        <v>36</v>
+      </c>
+      <c r="D76" s="65"/>
+      <c r="E76" s="38" t="s">
         <v>154</v>
       </c>
-      <c r="F71" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="G71" s="34"/>
-      <c r="H71" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="I71" s="34"/>
-    </row>
-    <row r="72" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="B72" s="34"/>
-      <c r="C72" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="D72" s="34"/>
-      <c r="E72" s="90" t="s">
+      <c r="F76" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="G76" s="65"/>
+      <c r="H76" s="65" t="s">
+        <v>58</v>
+      </c>
+      <c r="I76" s="65"/>
+    </row>
+    <row r="77" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="65" t="s">
+        <v>26</v>
+      </c>
+      <c r="B77" s="65"/>
+      <c r="C77" s="65" t="s">
+        <v>37</v>
+      </c>
+      <c r="D77" s="65"/>
+      <c r="E77" s="38" t="s">
         <v>155</v>
       </c>
-      <c r="F72" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="G72" s="34"/>
-      <c r="H72" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="I72" s="34"/>
-    </row>
-    <row r="73" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="B73" s="34"/>
-      <c r="C73" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="D73" s="39"/>
-      <c r="E73" s="90" t="s">
+      <c r="F77" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="G77" s="65"/>
+      <c r="H77" s="66" t="s">
+        <v>59</v>
+      </c>
+      <c r="I77" s="66"/>
+    </row>
+    <row r="78" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="65" t="s">
+        <v>27</v>
+      </c>
+      <c r="B78" s="65"/>
+      <c r="C78" s="65" t="s">
+        <v>38</v>
+      </c>
+      <c r="D78" s="65"/>
+      <c r="E78" s="38" t="s">
         <v>156</v>
       </c>
-      <c r="F73" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="G73" s="34"/>
-      <c r="H73" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="I73" s="34"/>
-    </row>
-    <row r="74" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="B74" s="34"/>
-      <c r="C74" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D74" s="34"/>
-      <c r="E74" s="90" t="s">
+      <c r="F78" s="77" t="s">
+        <v>49</v>
+      </c>
+      <c r="G78" s="77"/>
+      <c r="H78" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="I78" s="77"/>
+    </row>
+    <row r="79" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="65" t="s">
+        <v>28</v>
+      </c>
+      <c r="B79" s="65"/>
+      <c r="C79" s="65" t="s">
+        <v>39</v>
+      </c>
+      <c r="D79" s="65"/>
+      <c r="E79" s="38" t="s">
         <v>157</v>
       </c>
-      <c r="F74" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="G74" s="34"/>
-      <c r="H74" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="I74" s="34"/>
-    </row>
-    <row r="75" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="B75" s="34"/>
-      <c r="C75" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="D75" s="34"/>
-      <c r="E75" s="90" t="s">
+      <c r="F79" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="G79" s="65"/>
+      <c r="H79" s="66" t="s">
+        <v>61</v>
+      </c>
+      <c r="I79" s="66"/>
+    </row>
+    <row r="80" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="65" t="s">
+        <v>108</v>
+      </c>
+      <c r="B80" s="65"/>
+      <c r="C80" s="65" t="s">
+        <v>109</v>
+      </c>
+      <c r="D80" s="65"/>
+      <c r="E80" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="F75" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="G75" s="34"/>
-      <c r="H75" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="I75" s="34"/>
-    </row>
-    <row r="76" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="B76" s="34"/>
-      <c r="C76" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="D76" s="34"/>
-      <c r="E76" s="90" t="s">
-        <v>159</v>
-      </c>
-      <c r="F76" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="G76" s="34"/>
-      <c r="H76" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="I76" s="34"/>
-    </row>
-    <row r="77" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="B77" s="34"/>
-      <c r="C77" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="D77" s="34"/>
-      <c r="E77" s="90" t="s">
-        <v>160</v>
-      </c>
-      <c r="F77" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="G77" s="34"/>
-      <c r="H77" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="I77" s="38"/>
-    </row>
-    <row r="78" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="B78" s="34"/>
-      <c r="C78" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="D78" s="34"/>
-      <c r="E78" s="90" t="s">
-        <v>161</v>
-      </c>
-      <c r="F78" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="G78" s="39"/>
-      <c r="H78" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="I78" s="39"/>
-    </row>
-    <row r="79" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="B79" s="34"/>
-      <c r="C79" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="D79" s="34"/>
-      <c r="E79" s="90" t="s">
-        <v>162</v>
-      </c>
-      <c r="F79" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="G79" s="34"/>
-      <c r="H79" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="I79" s="38"/>
-    </row>
-    <row r="80" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="B80" s="34"/>
-      <c r="C80" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="D80" s="34"/>
-      <c r="E80" s="90" t="s">
-        <v>163</v>
-      </c>
-      <c r="F80" s="34" t="s">
+      <c r="F80" s="65" t="s">
         <v>110</v>
       </c>
-      <c r="G80" s="34"/>
-      <c r="H80" s="38" t="s">
+      <c r="G80" s="65"/>
+      <c r="H80" s="66" t="s">
         <v>111</v>
       </c>
-      <c r="I80" s="38"/>
+      <c r="I80" s="66"/>
     </row>
     <row r="81" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
@@ -2990,299 +2965,299 @@
       <c r="I81" s="4"/>
     </row>
     <row r="82" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="55" t="s">
+      <c r="A82" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="B82" s="56"/>
-      <c r="C82" s="55" t="s">
+      <c r="B82" s="46"/>
+      <c r="C82" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="D82" s="56"/>
-      <c r="E82" s="67" t="s">
+      <c r="D82" s="46"/>
+      <c r="E82" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="F82" s="55" t="s">
+      <c r="F82" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="G82" s="56"/>
-      <c r="H82" s="61" t="s">
+      <c r="G82" s="46"/>
+      <c r="H82" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="I82" s="62"/>
+      <c r="I82" s="60"/>
     </row>
     <row r="83" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="57"/>
       <c r="B83" s="58"/>
       <c r="C83" s="57"/>
       <c r="D83" s="58"/>
-      <c r="E83" s="68"/>
+      <c r="E83" s="56"/>
       <c r="F83" s="57"/>
       <c r="G83" s="58"/>
-      <c r="H83" s="63"/>
-      <c r="I83" s="64"/>
+      <c r="H83" s="61"/>
+      <c r="I83" s="62"/>
     </row>
     <row r="84" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="59"/>
-      <c r="B84" s="60"/>
-      <c r="C84" s="59"/>
-      <c r="D84" s="60"/>
-      <c r="E84" s="69"/>
-      <c r="F84" s="59"/>
-      <c r="G84" s="60"/>
-      <c r="H84" s="65"/>
-      <c r="I84" s="66"/>
+      <c r="A84" s="47"/>
+      <c r="B84" s="48"/>
+      <c r="C84" s="47"/>
+      <c r="D84" s="48"/>
+      <c r="E84" s="53"/>
+      <c r="F84" s="47"/>
+      <c r="G84" s="48"/>
+      <c r="H84" s="63"/>
+      <c r="I84" s="64"/>
     </row>
     <row r="85" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="34" t="s">
+      <c r="A85" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="B85" s="34"/>
-      <c r="C85" s="34" t="s">
+      <c r="B85" s="65"/>
+      <c r="C85" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="D85" s="34"/>
-      <c r="E85" s="90" t="s">
+      <c r="D85" s="65"/>
+      <c r="E85" s="38" t="s">
+        <v>159</v>
+      </c>
+      <c r="F85" s="65" t="s">
+        <v>40</v>
+      </c>
+      <c r="G85" s="65"/>
+      <c r="H85" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="I85" s="66"/>
+    </row>
+    <row r="86" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="65" t="s">
+        <v>19</v>
+      </c>
+      <c r="B86" s="65"/>
+      <c r="C86" s="77" t="s">
+        <v>30</v>
+      </c>
+      <c r="D86" s="77"/>
+      <c r="E86" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="F86" s="65" t="s">
+        <v>41</v>
+      </c>
+      <c r="G86" s="65"/>
+      <c r="H86" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="I86" s="66"/>
+    </row>
+    <row r="87" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="65" t="s">
+        <v>20</v>
+      </c>
+      <c r="B87" s="65"/>
+      <c r="C87" s="65" t="s">
+        <v>31</v>
+      </c>
+      <c r="D87" s="65"/>
+      <c r="E87" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="F87" s="65" t="s">
+        <v>42</v>
+      </c>
+      <c r="G87" s="65"/>
+      <c r="H87" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="I87" s="65"/>
+    </row>
+    <row r="88" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="65" t="s">
+        <v>21</v>
+      </c>
+      <c r="B88" s="65"/>
+      <c r="C88" s="65" t="s">
+        <v>32</v>
+      </c>
+      <c r="D88" s="65"/>
+      <c r="E88" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="F88" s="65" t="s">
+        <v>43</v>
+      </c>
+      <c r="G88" s="65"/>
+      <c r="H88" s="65" t="s">
+        <v>54</v>
+      </c>
+      <c r="I88" s="65"/>
+    </row>
+    <row r="89" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="B89" s="65"/>
+      <c r="C89" s="77" t="s">
+        <v>33</v>
+      </c>
+      <c r="D89" s="77"/>
+      <c r="E89" s="38" t="s">
+        <v>163</v>
+      </c>
+      <c r="F89" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="G89" s="65"/>
+      <c r="H89" s="65" t="s">
+        <v>55</v>
+      </c>
+      <c r="I89" s="65"/>
+    </row>
+    <row r="90" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="65" t="s">
+        <v>23</v>
+      </c>
+      <c r="B90" s="65"/>
+      <c r="C90" s="65" t="s">
+        <v>34</v>
+      </c>
+      <c r="D90" s="65"/>
+      <c r="E90" s="38" t="s">
         <v>164</v>
       </c>
-      <c r="F85" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="G85" s="34"/>
-      <c r="H85" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="I85" s="38"/>
-    </row>
-    <row r="86" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="B86" s="34"/>
-      <c r="C86" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="D86" s="39"/>
-      <c r="E86" s="90" t="s">
+      <c r="F90" s="65" t="s">
+        <v>45</v>
+      </c>
+      <c r="G90" s="65"/>
+      <c r="H90" s="65" t="s">
+        <v>56</v>
+      </c>
+      <c r="I90" s="65"/>
+    </row>
+    <row r="91" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="B91" s="65"/>
+      <c r="C91" s="65" t="s">
+        <v>35</v>
+      </c>
+      <c r="D91" s="65"/>
+      <c r="E91" s="38" t="s">
         <v>165</v>
       </c>
-      <c r="F86" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="G86" s="34"/>
-      <c r="H86" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="I86" s="38"/>
-    </row>
-    <row r="87" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="B87" s="34"/>
-      <c r="C87" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="D87" s="34"/>
-      <c r="E87" s="90" t="s">
+      <c r="F91" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="G91" s="65"/>
+      <c r="H91" s="65" t="s">
+        <v>57</v>
+      </c>
+      <c r="I91" s="65"/>
+    </row>
+    <row r="92" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="B92" s="65"/>
+      <c r="C92" s="65" t="s">
+        <v>36</v>
+      </c>
+      <c r="D92" s="65"/>
+      <c r="E92" s="38" t="s">
         <v>166</v>
       </c>
-      <c r="F87" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="G87" s="34"/>
-      <c r="H87" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="I87" s="34"/>
-    </row>
-    <row r="88" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="B88" s="34"/>
-      <c r="C88" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="D88" s="34"/>
-      <c r="E88" s="90" t="s">
+      <c r="F92" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="G92" s="65"/>
+      <c r="H92" s="65" t="s">
+        <v>58</v>
+      </c>
+      <c r="I92" s="65"/>
+    </row>
+    <row r="93" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="65" t="s">
+        <v>26</v>
+      </c>
+      <c r="B93" s="65"/>
+      <c r="C93" s="65" t="s">
+        <v>37</v>
+      </c>
+      <c r="D93" s="65"/>
+      <c r="E93" s="38" t="s">
         <v>167</v>
       </c>
-      <c r="F88" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="G88" s="34"/>
-      <c r="H88" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="I88" s="34"/>
-    </row>
-    <row r="89" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="B89" s="34"/>
-      <c r="C89" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="D89" s="39"/>
-      <c r="E89" s="90" t="s">
+      <c r="F93" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="G93" s="65"/>
+      <c r="H93" s="66" t="s">
+        <v>59</v>
+      </c>
+      <c r="I93" s="66"/>
+    </row>
+    <row r="94" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="65" t="s">
+        <v>27</v>
+      </c>
+      <c r="B94" s="65"/>
+      <c r="C94" s="65" t="s">
+        <v>38</v>
+      </c>
+      <c r="D94" s="65"/>
+      <c r="E94" s="38" t="s">
         <v>168</v>
       </c>
-      <c r="F89" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="G89" s="34"/>
-      <c r="H89" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="I89" s="34"/>
-    </row>
-    <row r="90" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="B90" s="34"/>
-      <c r="C90" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D90" s="34"/>
-      <c r="E90" s="90" t="s">
+      <c r="F94" s="77" t="s">
+        <v>49</v>
+      </c>
+      <c r="G94" s="77"/>
+      <c r="H94" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="I94" s="77"/>
+    </row>
+    <row r="95" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="65" t="s">
+        <v>28</v>
+      </c>
+      <c r="B95" s="65"/>
+      <c r="C95" s="65" t="s">
+        <v>39</v>
+      </c>
+      <c r="D95" s="65"/>
+      <c r="E95" s="38" t="s">
         <v>169</v>
       </c>
-      <c r="F90" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="G90" s="34"/>
-      <c r="H90" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="I90" s="34"/>
-    </row>
-    <row r="91" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="B91" s="34"/>
-      <c r="C91" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="D91" s="34"/>
-      <c r="E91" s="90" t="s">
+      <c r="F95" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="G95" s="65"/>
+      <c r="H95" s="66" t="s">
+        <v>61</v>
+      </c>
+      <c r="I95" s="66"/>
+    </row>
+    <row r="96" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="65" t="s">
+        <v>108</v>
+      </c>
+      <c r="B96" s="65"/>
+      <c r="C96" s="65" t="s">
+        <v>109</v>
+      </c>
+      <c r="D96" s="65"/>
+      <c r="E96" s="38" t="s">
         <v>170</v>
       </c>
-      <c r="F91" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="G91" s="34"/>
-      <c r="H91" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="I91" s="34"/>
-    </row>
-    <row r="92" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="B92" s="34"/>
-      <c r="C92" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="D92" s="34"/>
-      <c r="E92" s="90" t="s">
-        <v>171</v>
-      </c>
-      <c r="F92" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="G92" s="34"/>
-      <c r="H92" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="I92" s="34"/>
-    </row>
-    <row r="93" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="B93" s="34"/>
-      <c r="C93" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="D93" s="34"/>
-      <c r="E93" s="90" t="s">
-        <v>172</v>
-      </c>
-      <c r="F93" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="G93" s="34"/>
-      <c r="H93" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="I93" s="38"/>
-    </row>
-    <row r="94" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="B94" s="34"/>
-      <c r="C94" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="D94" s="34"/>
-      <c r="E94" s="90" t="s">
-        <v>173</v>
-      </c>
-      <c r="F94" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="G94" s="39"/>
-      <c r="H94" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="I94" s="39"/>
-    </row>
-    <row r="95" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="B95" s="34"/>
-      <c r="C95" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="D95" s="34"/>
-      <c r="E95" s="90" t="s">
-        <v>174</v>
-      </c>
-      <c r="F95" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="G95" s="34"/>
-      <c r="H95" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="I95" s="38"/>
-    </row>
-    <row r="96" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="B96" s="34"/>
-      <c r="C96" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="D96" s="34"/>
-      <c r="E96" s="90" t="s">
-        <v>175</v>
-      </c>
-      <c r="F96" s="34" t="s">
+      <c r="F96" s="65" t="s">
         <v>110</v>
       </c>
-      <c r="G96" s="34"/>
-      <c r="H96" s="38" t="s">
+      <c r="G96" s="65"/>
+      <c r="H96" s="66" t="s">
         <v>111</v>
       </c>
-      <c r="I96" s="38"/>
+      <c r="I96" s="66"/>
     </row>
     <row r="97" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="30"/>
@@ -3296,260 +3271,260 @@
       <c r="I97" s="9"/>
     </row>
     <row r="98" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="B98" s="51"/>
-      <c r="C98" s="51"/>
-      <c r="D98" s="51"/>
-      <c r="E98" s="51"/>
-      <c r="F98" s="51"/>
-      <c r="G98" s="51"/>
-      <c r="H98" s="51"/>
-      <c r="I98" s="51"/>
+      <c r="A98" s="49" t="s">
+        <v>195</v>
+      </c>
+      <c r="B98" s="49"/>
+      <c r="C98" s="49"/>
+      <c r="D98" s="49"/>
+      <c r="E98" s="49"/>
+      <c r="F98" s="49"/>
+      <c r="G98" s="49"/>
+      <c r="H98" s="49"/>
+      <c r="I98" s="49"/>
     </row>
     <row r="99" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="67" t="s">
+      <c r="A99" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="B99" s="67" t="s">
+      <c r="B99" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="C99" s="80" t="s">
+      <c r="C99" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="D99" s="55" t="s">
+      <c r="D99" s="45" t="s">
         <v>118</v>
       </c>
-      <c r="E99" s="56"/>
-      <c r="F99" s="55" t="s">
+      <c r="E99" s="46"/>
+      <c r="F99" s="45" t="s">
         <v>119</v>
       </c>
-      <c r="G99" s="56"/>
-      <c r="H99" s="55" t="s">
+      <c r="G99" s="46"/>
+      <c r="H99" s="45" t="s">
         <v>112</v>
       </c>
-      <c r="I99" s="56"/>
+      <c r="I99" s="46"/>
     </row>
     <row r="100" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="69"/>
-      <c r="B100" s="69"/>
-      <c r="C100" s="81"/>
-      <c r="D100" s="59"/>
-      <c r="E100" s="60"/>
-      <c r="F100" s="59"/>
-      <c r="G100" s="60"/>
-      <c r="H100" s="59"/>
-      <c r="I100" s="60"/>
+      <c r="A100" s="53"/>
+      <c r="B100" s="53"/>
+      <c r="C100" s="51"/>
+      <c r="D100" s="47"/>
+      <c r="E100" s="48"/>
+      <c r="F100" s="47"/>
+      <c r="G100" s="48"/>
+      <c r="H100" s="47"/>
+      <c r="I100" s="48"/>
     </row>
     <row r="101" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="76">
+      <c r="A101" s="75">
         <v>1</v>
       </c>
-      <c r="B101" s="67" t="s">
+      <c r="B101" s="52" t="s">
         <v>25</v>
       </c>
       <c r="C101" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="D101" s="91" t="s">
-        <v>176</v>
-      </c>
-      <c r="E101" s="92"/>
-      <c r="F101" s="91" t="s">
-        <v>177</v>
-      </c>
-      <c r="G101" s="92"/>
-      <c r="H101" s="36" t="s">
+      <c r="D101" s="54" t="s">
+        <v>171</v>
+      </c>
+      <c r="E101" s="55"/>
+      <c r="F101" s="54" t="s">
+        <v>172</v>
+      </c>
+      <c r="G101" s="55"/>
+      <c r="H101" s="72" t="s">
         <v>113</v>
       </c>
-      <c r="I101" s="36"/>
+      <c r="I101" s="72"/>
     </row>
     <row r="102" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="77"/>
-      <c r="B102" s="68"/>
+      <c r="A102" s="76"/>
+      <c r="B102" s="56"/>
       <c r="C102" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="D102" s="91" t="s">
-        <v>178</v>
-      </c>
-      <c r="E102" s="92"/>
-      <c r="F102" s="91" t="s">
-        <v>179</v>
-      </c>
-      <c r="G102" s="92"/>
-      <c r="H102" s="36"/>
-      <c r="I102" s="36"/>
+      <c r="D102" s="54" t="s">
+        <v>173</v>
+      </c>
+      <c r="E102" s="55"/>
+      <c r="F102" s="54" t="s">
+        <v>174</v>
+      </c>
+      <c r="G102" s="55"/>
+      <c r="H102" s="72"/>
+      <c r="I102" s="72"/>
     </row>
     <row r="103" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="76">
+      <c r="A103" s="75">
         <v>2</v>
       </c>
-      <c r="B103" s="68"/>
+      <c r="B103" s="56"/>
       <c r="C103" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="D103" s="91" t="s">
-        <v>180</v>
-      </c>
-      <c r="E103" s="92"/>
-      <c r="F103" s="91" t="s">
-        <v>186</v>
-      </c>
-      <c r="G103" s="92"/>
-      <c r="H103" s="36"/>
-      <c r="I103" s="36"/>
+      <c r="D103" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="E103" s="55"/>
+      <c r="F103" s="54" t="s">
+        <v>181</v>
+      </c>
+      <c r="G103" s="55"/>
+      <c r="H103" s="72"/>
+      <c r="I103" s="72"/>
     </row>
     <row r="104" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="77"/>
-      <c r="B104" s="68"/>
+      <c r="A104" s="76"/>
+      <c r="B104" s="56"/>
       <c r="C104" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="D104" s="91" t="s">
-        <v>181</v>
-      </c>
-      <c r="E104" s="92"/>
-      <c r="F104" s="91" t="s">
-        <v>187</v>
-      </c>
-      <c r="G104" s="92"/>
-      <c r="H104" s="36"/>
-      <c r="I104" s="36"/>
+      <c r="D104" s="54" t="s">
+        <v>176</v>
+      </c>
+      <c r="E104" s="55"/>
+      <c r="F104" s="54" t="s">
+        <v>182</v>
+      </c>
+      <c r="G104" s="55"/>
+      <c r="H104" s="72"/>
+      <c r="I104" s="72"/>
     </row>
     <row r="105" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="76">
+      <c r="A105" s="75">
         <v>3</v>
       </c>
-      <c r="B105" s="68"/>
+      <c r="B105" s="56"/>
       <c r="C105" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="D105" s="91" t="s">
-        <v>182</v>
-      </c>
-      <c r="E105" s="92"/>
-      <c r="F105" s="91" t="s">
-        <v>188</v>
-      </c>
-      <c r="G105" s="92"/>
-      <c r="H105" s="36"/>
-      <c r="I105" s="36"/>
+      <c r="D105" s="54" t="s">
+        <v>177</v>
+      </c>
+      <c r="E105" s="55"/>
+      <c r="F105" s="54" t="s">
+        <v>183</v>
+      </c>
+      <c r="G105" s="55"/>
+      <c r="H105" s="72"/>
+      <c r="I105" s="72"/>
     </row>
     <row r="106" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="77"/>
-      <c r="B106" s="68"/>
+      <c r="A106" s="76"/>
+      <c r="B106" s="56"/>
       <c r="C106" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="D106" s="91" t="s">
-        <v>183</v>
-      </c>
-      <c r="E106" s="92"/>
-      <c r="F106" s="91" t="s">
-        <v>189</v>
-      </c>
-      <c r="G106" s="92"/>
-      <c r="H106" s="36"/>
-      <c r="I106" s="36"/>
+      <c r="D106" s="54" t="s">
+        <v>178</v>
+      </c>
+      <c r="E106" s="55"/>
+      <c r="F106" s="54" t="s">
+        <v>184</v>
+      </c>
+      <c r="G106" s="55"/>
+      <c r="H106" s="72"/>
+      <c r="I106" s="72"/>
     </row>
     <row r="107" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="76">
+      <c r="A107" s="75">
         <v>4</v>
       </c>
-      <c r="B107" s="68"/>
+      <c r="B107" s="56"/>
       <c r="C107" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="D107" s="91" t="s">
-        <v>184</v>
-      </c>
-      <c r="E107" s="92"/>
-      <c r="F107" s="91" t="s">
-        <v>190</v>
-      </c>
-      <c r="G107" s="92"/>
-      <c r="H107" s="36"/>
-      <c r="I107" s="36"/>
+      <c r="D107" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="E107" s="55"/>
+      <c r="F107" s="54" t="s">
+        <v>185</v>
+      </c>
+      <c r="G107" s="55"/>
+      <c r="H107" s="72"/>
+      <c r="I107" s="72"/>
     </row>
     <row r="108" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="77"/>
-      <c r="B108" s="69"/>
+      <c r="A108" s="76"/>
+      <c r="B108" s="53"/>
       <c r="C108" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="D108" s="91" t="s">
-        <v>185</v>
-      </c>
-      <c r="E108" s="92"/>
-      <c r="F108" s="91" t="s">
-        <v>191</v>
-      </c>
-      <c r="G108" s="92"/>
-      <c r="H108" s="36"/>
-      <c r="I108" s="36"/>
+      <c r="D108" s="54" t="s">
+        <v>180</v>
+      </c>
+      <c r="E108" s="55"/>
+      <c r="F108" s="54" t="s">
+        <v>186</v>
+      </c>
+      <c r="G108" s="55"/>
+      <c r="H108" s="72"/>
+      <c r="I108" s="72"/>
     </row>
     <row r="109" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="28"/>
       <c r="B109" s="29"/>
       <c r="C109" s="29"/>
-      <c r="D109" s="93"/>
-      <c r="E109" s="93"/>
-      <c r="F109" s="93"/>
-      <c r="G109" s="93"/>
+      <c r="D109" s="39"/>
+      <c r="E109" s="39"/>
+      <c r="F109" s="39"/>
+      <c r="G109" s="39"/>
       <c r="H109" s="29"/>
       <c r="I109" s="29"/>
     </row>
     <row r="110" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="51" t="s">
-        <v>203</v>
-      </c>
-      <c r="B110" s="51"/>
-      <c r="C110" s="51"/>
-      <c r="D110" s="51"/>
-      <c r="E110" s="51"/>
-      <c r="F110" s="51"/>
-      <c r="G110" s="51"/>
-      <c r="H110" s="51"/>
-      <c r="I110" s="51"/>
+      <c r="A110" s="49" t="s">
+        <v>198</v>
+      </c>
+      <c r="B110" s="49"/>
+      <c r="C110" s="49"/>
+      <c r="D110" s="49"/>
+      <c r="E110" s="49"/>
+      <c r="F110" s="49"/>
+      <c r="G110" s="49"/>
+      <c r="H110" s="49"/>
+      <c r="I110" s="49"/>
     </row>
     <row r="111" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="51"/>
-      <c r="B111" s="51"/>
-      <c r="C111" s="51"/>
-      <c r="D111" s="51"/>
-      <c r="E111" s="51"/>
-      <c r="F111" s="51"/>
-      <c r="G111" s="51"/>
-      <c r="H111" s="51"/>
-      <c r="I111" s="51"/>
+      <c r="A111" s="49"/>
+      <c r="B111" s="49"/>
+      <c r="C111" s="49"/>
+      <c r="D111" s="49"/>
+      <c r="E111" s="49"/>
+      <c r="F111" s="49"/>
+      <c r="G111" s="49"/>
+      <c r="H111" s="49"/>
+      <c r="I111" s="49"/>
     </row>
     <row r="112" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="51"/>
-      <c r="B112" s="51"/>
-      <c r="C112" s="51"/>
-      <c r="D112" s="51"/>
-      <c r="E112" s="51"/>
-      <c r="F112" s="51"/>
-      <c r="G112" s="51"/>
-      <c r="H112" s="51"/>
-      <c r="I112" s="51"/>
+      <c r="A112" s="49"/>
+      <c r="B112" s="49"/>
+      <c r="C112" s="49"/>
+      <c r="D112" s="49"/>
+      <c r="E112" s="49"/>
+      <c r="F112" s="49"/>
+      <c r="G112" s="49"/>
+      <c r="H112" s="49"/>
+      <c r="I112" s="49"/>
     </row>
     <row r="113" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="28"/>
       <c r="B113" s="29"/>
       <c r="C113" s="29"/>
-      <c r="D113" s="93"/>
-      <c r="E113" s="93"/>
-      <c r="F113" s="93"/>
-      <c r="G113" s="93"/>
+      <c r="D113" s="39"/>
+      <c r="E113" s="39"/>
+      <c r="F113" s="39"/>
+      <c r="G113" s="39"/>
       <c r="H113" s="29"/>
       <c r="I113" s="29"/>
     </row>
     <row r="114" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="33" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B114" s="33"/>
       <c r="C114" s="33"/>
@@ -3561,32 +3536,32 @@
       <c r="I114" s="1"/>
     </row>
     <row r="115" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="67" t="s">
+      <c r="A115" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="B115" s="55" t="s">
+      <c r="B115" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="C115" s="56"/>
-      <c r="D115" s="55" t="s">
+      <c r="C115" s="46"/>
+      <c r="D115" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="E115" s="56"/>
-      <c r="F115" s="55" t="s">
+      <c r="E115" s="46"/>
+      <c r="F115" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="G115" s="56"/>
-      <c r="H115" s="35"/>
-      <c r="I115" s="35"/>
+      <c r="G115" s="46"/>
+      <c r="H115" s="69"/>
+      <c r="I115" s="69"/>
     </row>
     <row r="116" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="69"/>
-      <c r="B116" s="59"/>
-      <c r="C116" s="60"/>
-      <c r="D116" s="59"/>
-      <c r="E116" s="60"/>
-      <c r="F116" s="59"/>
-      <c r="G116" s="60"/>
+      <c r="A116" s="53"/>
+      <c r="B116" s="47"/>
+      <c r="C116" s="48"/>
+      <c r="D116" s="47"/>
+      <c r="E116" s="48"/>
+      <c r="F116" s="47"/>
+      <c r="G116" s="48"/>
       <c r="H116" s="30"/>
       <c r="I116" s="30"/>
     </row>
@@ -3594,69 +3569,69 @@
       <c r="A117" s="10">
         <v>1</v>
       </c>
-      <c r="B117" s="36">
+      <c r="B117" s="72">
         <v>1000</v>
       </c>
-      <c r="C117" s="36"/>
-      <c r="D117" s="36" t="s">
+      <c r="C117" s="72"/>
+      <c r="D117" s="72" t="s">
         <v>68</v>
       </c>
-      <c r="E117" s="36"/>
-      <c r="F117" s="94">
+      <c r="E117" s="72"/>
+      <c r="F117" s="71">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G117" s="94"/>
-      <c r="H117" s="35"/>
-      <c r="I117" s="35"/>
+      <c r="G117" s="71"/>
+      <c r="H117" s="69"/>
+      <c r="I117" s="69"/>
     </row>
     <row r="118" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="10">
         <v>2</v>
       </c>
-      <c r="B118" s="36"/>
-      <c r="C118" s="36"/>
-      <c r="D118" s="36"/>
-      <c r="E118" s="36"/>
-      <c r="F118" s="94">
+      <c r="B118" s="72"/>
+      <c r="C118" s="72"/>
+      <c r="D118" s="72"/>
+      <c r="E118" s="72"/>
+      <c r="F118" s="71">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G118" s="94"/>
-      <c r="H118" s="35"/>
-      <c r="I118" s="35"/>
+      <c r="G118" s="71"/>
+      <c r="H118" s="69"/>
+      <c r="I118" s="69"/>
     </row>
     <row r="119" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="10">
         <v>3</v>
       </c>
-      <c r="B119" s="36"/>
-      <c r="C119" s="36"/>
-      <c r="D119" s="36"/>
-      <c r="E119" s="36"/>
-      <c r="F119" s="94">
+      <c r="B119" s="72"/>
+      <c r="C119" s="72"/>
+      <c r="D119" s="72"/>
+      <c r="E119" s="72"/>
+      <c r="F119" s="71">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G119" s="94"/>
-      <c r="H119" s="35"/>
-      <c r="I119" s="35"/>
+      <c r="G119" s="71"/>
+      <c r="H119" s="69"/>
+      <c r="I119" s="69"/>
     </row>
     <row r="120" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="10">
         <v>4</v>
       </c>
-      <c r="B120" s="36"/>
-      <c r="C120" s="36"/>
-      <c r="D120" s="36"/>
-      <c r="E120" s="36"/>
-      <c r="F120" s="94">
+      <c r="B120" s="72"/>
+      <c r="C120" s="72"/>
+      <c r="D120" s="72"/>
+      <c r="E120" s="72"/>
+      <c r="F120" s="71">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G120" s="94"/>
-      <c r="H120" s="35"/>
-      <c r="I120" s="35"/>
+      <c r="G120" s="71"/>
+      <c r="H120" s="69"/>
+      <c r="I120" s="69"/>
     </row>
     <row r="121" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="27" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B121" s="27"/>
       <c r="C121" s="27"/>
@@ -3679,40 +3654,40 @@
       <c r="I122" s="30"/>
     </row>
     <row r="123" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="37" t="s">
-        <v>199</v>
-      </c>
-      <c r="B123" s="37"/>
-      <c r="C123" s="37"/>
-      <c r="D123" s="37"/>
-      <c r="E123" s="37"/>
-      <c r="F123" s="37"/>
-      <c r="G123" s="37"/>
-      <c r="H123" s="37"/>
-      <c r="I123" s="37"/>
+      <c r="A123" s="70" t="s">
+        <v>194</v>
+      </c>
+      <c r="B123" s="70"/>
+      <c r="C123" s="70"/>
+      <c r="D123" s="70"/>
+      <c r="E123" s="70"/>
+      <c r="F123" s="70"/>
+      <c r="G123" s="70"/>
+      <c r="H123" s="70"/>
+      <c r="I123" s="70"/>
     </row>
     <row r="124" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="70" t="s">
+      <c r="A124" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="B124" s="71"/>
-      <c r="C124" s="55" t="s">
+      <c r="B124" s="42"/>
+      <c r="C124" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="D124" s="56"/>
-      <c r="E124" s="55" t="s">
+      <c r="D124" s="46"/>
+      <c r="E124" s="45" t="s">
         <v>73</v>
       </c>
-      <c r="F124" s="56"/>
-      <c r="G124" s="55" t="s">
+      <c r="F124" s="46"/>
+      <c r="G124" s="45" t="s">
         <v>74</v>
       </c>
-      <c r="H124" s="56"/>
+      <c r="H124" s="46"/>
       <c r="I124" s="30"/>
     </row>
     <row r="125" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="74"/>
-      <c r="B125" s="75"/>
+      <c r="A125" s="73"/>
+      <c r="B125" s="74"/>
       <c r="C125" s="57"/>
       <c r="D125" s="58"/>
       <c r="E125" s="57"/>
@@ -3722,139 +3697,139 @@
       <c r="I125" s="30"/>
     </row>
     <row r="126" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="72"/>
-      <c r="B126" s="73"/>
-      <c r="C126" s="59"/>
-      <c r="D126" s="60"/>
-      <c r="E126" s="59"/>
-      <c r="F126" s="60"/>
-      <c r="G126" s="59"/>
-      <c r="H126" s="60"/>
+      <c r="A126" s="43"/>
+      <c r="B126" s="44"/>
+      <c r="C126" s="47"/>
+      <c r="D126" s="48"/>
+      <c r="E126" s="47"/>
+      <c r="F126" s="48"/>
+      <c r="G126" s="47"/>
+      <c r="H126" s="48"/>
       <c r="I126" s="30"/>
     </row>
     <row r="127" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="70" t="s">
+      <c r="A127" s="41" t="s">
         <v>75</v>
       </c>
-      <c r="B127" s="71"/>
-      <c r="C127" s="70" t="s">
+      <c r="B127" s="42"/>
+      <c r="C127" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="D127" s="71"/>
-      <c r="E127" s="55" t="s">
+      <c r="D127" s="42"/>
+      <c r="E127" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="F127" s="56"/>
-      <c r="G127" s="55" t="s">
+      <c r="F127" s="46"/>
+      <c r="G127" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H127" s="56"/>
+      <c r="H127" s="46"/>
       <c r="I127" s="30"/>
     </row>
     <row r="128" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="72"/>
-      <c r="B128" s="73"/>
-      <c r="C128" s="72"/>
-      <c r="D128" s="73"/>
-      <c r="E128" s="59"/>
-      <c r="F128" s="60"/>
-      <c r="G128" s="59"/>
-      <c r="H128" s="60"/>
+      <c r="A128" s="43"/>
+      <c r="B128" s="44"/>
+      <c r="C128" s="43"/>
+      <c r="D128" s="44"/>
+      <c r="E128" s="47"/>
+      <c r="F128" s="48"/>
+      <c r="G128" s="47"/>
+      <c r="H128" s="48"/>
       <c r="I128" s="30"/>
     </row>
     <row r="129" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="70" t="s">
+      <c r="A129" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="B129" s="71"/>
-      <c r="C129" s="70" t="s">
+      <c r="B129" s="42"/>
+      <c r="C129" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="D129" s="71"/>
-      <c r="E129" s="55" t="s">
+      <c r="D129" s="42"/>
+      <c r="E129" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="F129" s="56"/>
-      <c r="G129" s="55" t="s">
+      <c r="F129" s="46"/>
+      <c r="G129" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H129" s="56"/>
+      <c r="H129" s="46"/>
       <c r="I129" s="30"/>
     </row>
     <row r="130" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="72"/>
-      <c r="B130" s="73"/>
-      <c r="C130" s="72"/>
-      <c r="D130" s="73"/>
-      <c r="E130" s="59"/>
-      <c r="F130" s="60"/>
-      <c r="G130" s="59"/>
-      <c r="H130" s="60"/>
+      <c r="A130" s="43"/>
+      <c r="B130" s="44"/>
+      <c r="C130" s="43"/>
+      <c r="D130" s="44"/>
+      <c r="E130" s="47"/>
+      <c r="F130" s="48"/>
+      <c r="G130" s="47"/>
+      <c r="H130" s="48"/>
       <c r="I130" s="30"/>
     </row>
     <row r="131" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="70" t="s">
+      <c r="A131" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="B131" s="71"/>
-      <c r="C131" s="70" t="s">
+      <c r="B131" s="42"/>
+      <c r="C131" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="D131" s="71"/>
-      <c r="E131" s="55" t="s">
+      <c r="D131" s="42"/>
+      <c r="E131" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="F131" s="56"/>
-      <c r="G131" s="55" t="s">
+      <c r="F131" s="46"/>
+      <c r="G131" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H131" s="56"/>
+      <c r="H131" s="46"/>
       <c r="I131" s="30"/>
     </row>
     <row r="132" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="72"/>
-      <c r="B132" s="73"/>
-      <c r="C132" s="72"/>
-      <c r="D132" s="73"/>
-      <c r="E132" s="59"/>
-      <c r="F132" s="60"/>
-      <c r="G132" s="59"/>
-      <c r="H132" s="60"/>
+      <c r="A132" s="43"/>
+      <c r="B132" s="44"/>
+      <c r="C132" s="43"/>
+      <c r="D132" s="44"/>
+      <c r="E132" s="47"/>
+      <c r="F132" s="48"/>
+      <c r="G132" s="47"/>
+      <c r="H132" s="48"/>
       <c r="I132" s="30"/>
     </row>
     <row r="133" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="78"/>
-      <c r="B133" s="78"/>
-      <c r="C133" s="79"/>
-      <c r="D133" s="79"/>
-      <c r="E133" s="79"/>
-      <c r="F133" s="79"/>
-      <c r="G133" s="35"/>
-      <c r="H133" s="35"/>
+      <c r="A133" s="67"/>
+      <c r="B133" s="67"/>
+      <c r="C133" s="68"/>
+      <c r="D133" s="68"/>
+      <c r="E133" s="68"/>
+      <c r="F133" s="68"/>
+      <c r="G133" s="69"/>
+      <c r="H133" s="69"/>
       <c r="I133" s="30"/>
     </row>
     <row r="134" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="37" t="s">
-        <v>201</v>
-      </c>
-      <c r="B134" s="37"/>
-      <c r="C134" s="37"/>
-      <c r="D134" s="37"/>
-      <c r="E134" s="37"/>
-      <c r="F134" s="37"/>
-      <c r="G134" s="37"/>
-      <c r="H134" s="37"/>
-      <c r="I134" s="37"/>
+      <c r="A134" s="70" t="s">
+        <v>196</v>
+      </c>
+      <c r="B134" s="70"/>
+      <c r="C134" s="70"/>
+      <c r="D134" s="70"/>
+      <c r="E134" s="70"/>
+      <c r="F134" s="70"/>
+      <c r="G134" s="70"/>
+      <c r="H134" s="70"/>
+      <c r="I134" s="70"/>
     </row>
     <row r="135" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="78"/>
-      <c r="B135" s="78"/>
-      <c r="C135" s="79"/>
-      <c r="D135" s="79"/>
-      <c r="E135" s="79"/>
-      <c r="F135" s="79"/>
-      <c r="G135" s="35"/>
-      <c r="H135" s="35"/>
+      <c r="A135" s="67"/>
+      <c r="B135" s="67"/>
+      <c r="C135" s="68"/>
+      <c r="D135" s="68"/>
+      <c r="E135" s="68"/>
+      <c r="F135" s="68"/>
+      <c r="G135" s="69"/>
+      <c r="H135" s="69"/>
       <c r="I135" s="30"/>
     </row>
     <row r="136" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
@@ -3868,13 +3843,13 @@
       <c r="H136" s="1"/>
       <c r="I136" s="1"/>
     </row>
-    <row r="137" spans="1:9" s="95" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A137" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="B137" s="40"/>
+    <row r="137" spans="1:9" s="40" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A137" s="88" t="s">
+        <v>120</v>
+      </c>
+      <c r="B137" s="88"/>
       <c r="C137" s="23" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D137" s="21"/>
       <c r="E137" s="21"/>
@@ -3882,29 +3857,29 @@
       <c r="G137" s="1"/>
       <c r="H137" s="1"/>
     </row>
-    <row r="138" spans="1:9" s="95" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A138" s="40" t="s">
-        <v>127</v>
-      </c>
-      <c r="B138" s="40"/>
+    <row r="138" spans="1:9" s="40" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A138" s="88" t="s">
+        <v>122</v>
+      </c>
+      <c r="B138" s="88"/>
       <c r="C138" s="19"/>
       <c r="D138" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="E138" s="96" t="s">
+      <c r="E138" s="95" t="s">
         <v>105</v>
       </c>
-      <c r="F138" s="50"/>
+      <c r="F138" s="96"/>
       <c r="G138" s="21" t="s">
         <v>106</v>
       </c>
       <c r="H138" s="25"/>
     </row>
-    <row r="139" spans="1:9" s="95" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A139" s="40" t="s">
+    <row r="139" spans="1:9" s="40" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A139" s="88" t="s">
         <v>102</v>
       </c>
-      <c r="B139" s="40"/>
+      <c r="B139" s="88"/>
       <c r="C139" s="97" t="s">
         <v>103</v>
       </c>
@@ -3929,6 +3904,302 @@
     <row r="152" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="320">
+    <mergeCell ref="C139:D139"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="F118:G118"/>
+    <mergeCell ref="H118:I118"/>
+    <mergeCell ref="F119:G119"/>
+    <mergeCell ref="H119:I119"/>
+    <mergeCell ref="H120:I120"/>
+    <mergeCell ref="F120:G120"/>
+    <mergeCell ref="B117:C120"/>
+    <mergeCell ref="A123:I123"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="A139:B139"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="H57:I57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="A137:B137"/>
+    <mergeCell ref="A138:B138"/>
+    <mergeCell ref="E138:F138"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="A98:I98"/>
+    <mergeCell ref="H115:I115"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A34:B36"/>
+    <mergeCell ref="H34:I36"/>
+    <mergeCell ref="F34:G36"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="H66:I68"/>
+    <mergeCell ref="F66:G68"/>
+    <mergeCell ref="E66:E68"/>
+    <mergeCell ref="C66:D68"/>
+    <mergeCell ref="A66:B68"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="H69:I69"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="H70:I70"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="F71:G71"/>
+    <mergeCell ref="H71:I71"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="H78:I78"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="H79:I79"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="F77:G77"/>
+    <mergeCell ref="H77:I77"/>
+    <mergeCell ref="H92:I92"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="H85:I85"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="H80:I80"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="H86:I86"/>
+    <mergeCell ref="H82:I84"/>
+    <mergeCell ref="F82:G84"/>
+    <mergeCell ref="E82:E84"/>
+    <mergeCell ref="C82:D84"/>
+    <mergeCell ref="A82:B84"/>
+    <mergeCell ref="F102:G102"/>
+    <mergeCell ref="F103:G103"/>
+    <mergeCell ref="F104:G104"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="F94:G94"/>
+    <mergeCell ref="H94:I94"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="F89:G89"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="F91:G91"/>
+    <mergeCell ref="H91:I91"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="A127:B128"/>
+    <mergeCell ref="C131:D132"/>
+    <mergeCell ref="C129:D130"/>
+    <mergeCell ref="F93:G93"/>
+    <mergeCell ref="H93:I93"/>
+    <mergeCell ref="H117:I117"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="D117:E120"/>
+    <mergeCell ref="G124:H126"/>
+    <mergeCell ref="E124:F126"/>
+    <mergeCell ref="C124:D126"/>
+    <mergeCell ref="A124:B126"/>
+    <mergeCell ref="D102:E102"/>
+    <mergeCell ref="D101:E101"/>
+    <mergeCell ref="H101:I108"/>
+    <mergeCell ref="B101:B108"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="A103:A104"/>
+    <mergeCell ref="A105:A106"/>
+    <mergeCell ref="A107:A108"/>
+    <mergeCell ref="D103:E103"/>
+    <mergeCell ref="D104:E104"/>
+    <mergeCell ref="D108:E108"/>
+    <mergeCell ref="F101:G101"/>
+    <mergeCell ref="A135:B135"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="E135:F135"/>
+    <mergeCell ref="G135:H135"/>
+    <mergeCell ref="A133:B133"/>
+    <mergeCell ref="C133:D133"/>
+    <mergeCell ref="E133:F133"/>
+    <mergeCell ref="G133:H133"/>
+    <mergeCell ref="A134:I134"/>
+    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="C34:D36"/>
+    <mergeCell ref="H50:I52"/>
+    <mergeCell ref="F50:G52"/>
+    <mergeCell ref="E50:E52"/>
+    <mergeCell ref="C50:D52"/>
+    <mergeCell ref="A50:B52"/>
+    <mergeCell ref="F106:G106"/>
+    <mergeCell ref="F107:G107"/>
+    <mergeCell ref="D107:E107"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="F95:G95"/>
+    <mergeCell ref="H95:I95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="H96:I96"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="F90:G90"/>
+    <mergeCell ref="H90:I90"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="C91:D91"/>
     <mergeCell ref="C127:D128"/>
     <mergeCell ref="E131:F132"/>
     <mergeCell ref="E129:F130"/>
@@ -3953,302 +4224,6 @@
     <mergeCell ref="F108:G108"/>
     <mergeCell ref="A131:B132"/>
     <mergeCell ref="A129:B130"/>
-    <mergeCell ref="E34:E36"/>
-    <mergeCell ref="C34:D36"/>
-    <mergeCell ref="H50:I52"/>
-    <mergeCell ref="F50:G52"/>
-    <mergeCell ref="E50:E52"/>
-    <mergeCell ref="C50:D52"/>
-    <mergeCell ref="A50:B52"/>
-    <mergeCell ref="F106:G106"/>
-    <mergeCell ref="F107:G107"/>
-    <mergeCell ref="D107:E107"/>
-    <mergeCell ref="A95:B95"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="F95:G95"/>
-    <mergeCell ref="H95:I95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="H96:I96"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="F90:G90"/>
-    <mergeCell ref="H90:I90"/>
-    <mergeCell ref="A91:B91"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A135:B135"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="E135:F135"/>
-    <mergeCell ref="G135:H135"/>
-    <mergeCell ref="A133:B133"/>
-    <mergeCell ref="C133:D133"/>
-    <mergeCell ref="E133:F133"/>
-    <mergeCell ref="G133:H133"/>
-    <mergeCell ref="A134:I134"/>
-    <mergeCell ref="A127:B128"/>
-    <mergeCell ref="C131:D132"/>
-    <mergeCell ref="C129:D130"/>
-    <mergeCell ref="F93:G93"/>
-    <mergeCell ref="H93:I93"/>
-    <mergeCell ref="H117:I117"/>
-    <mergeCell ref="F117:G117"/>
-    <mergeCell ref="D117:E120"/>
-    <mergeCell ref="G124:H126"/>
-    <mergeCell ref="E124:F126"/>
-    <mergeCell ref="C124:D126"/>
-    <mergeCell ref="A124:B126"/>
-    <mergeCell ref="D102:E102"/>
-    <mergeCell ref="D101:E101"/>
-    <mergeCell ref="H101:I108"/>
-    <mergeCell ref="B101:B108"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="A103:A104"/>
-    <mergeCell ref="A105:A106"/>
-    <mergeCell ref="A107:A108"/>
-    <mergeCell ref="D103:E103"/>
-    <mergeCell ref="D104:E104"/>
-    <mergeCell ref="D108:E108"/>
-    <mergeCell ref="F101:G101"/>
-    <mergeCell ref="F102:G102"/>
-    <mergeCell ref="F103:G103"/>
-    <mergeCell ref="F104:G104"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="F94:G94"/>
-    <mergeCell ref="H94:I94"/>
-    <mergeCell ref="A87:B87"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="F89:G89"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="F91:G91"/>
-    <mergeCell ref="H91:I91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="F92:G92"/>
-    <mergeCell ref="H92:I92"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="F85:G85"/>
-    <mergeCell ref="H85:I85"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="H80:I80"/>
-    <mergeCell ref="A86:B86"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="F86:G86"/>
-    <mergeCell ref="H86:I86"/>
-    <mergeCell ref="H82:I84"/>
-    <mergeCell ref="F82:G84"/>
-    <mergeCell ref="E82:E84"/>
-    <mergeCell ref="C82:D84"/>
-    <mergeCell ref="A82:B84"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="F79:G79"/>
-    <mergeCell ref="H79:I79"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="F75:G75"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="F77:G77"/>
-    <mergeCell ref="H77:I77"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="H73:I73"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="H78:I78"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="H70:I70"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="F71:G71"/>
-    <mergeCell ref="H71:I71"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="F72:G72"/>
-    <mergeCell ref="H72:I72"/>
-    <mergeCell ref="H66:I68"/>
-    <mergeCell ref="F66:G68"/>
-    <mergeCell ref="E66:E68"/>
-    <mergeCell ref="C66:D68"/>
-    <mergeCell ref="A66:B68"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="H69:I69"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A7:I7"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A30:I30"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A34:B36"/>
-    <mergeCell ref="H34:I36"/>
-    <mergeCell ref="F34:G36"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="A98:I98"/>
-    <mergeCell ref="H115:I115"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="A139:B139"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="H57:I57"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="A137:B137"/>
-    <mergeCell ref="A138:B138"/>
-    <mergeCell ref="E138:F138"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="C139:D139"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="F118:G118"/>
-    <mergeCell ref="H118:I118"/>
-    <mergeCell ref="F119:G119"/>
-    <mergeCell ref="H119:I119"/>
-    <mergeCell ref="H120:I120"/>
-    <mergeCell ref="F120:G120"/>
-    <mergeCell ref="B117:C120"/>
-    <mergeCell ref="A123:I123"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="F59:G59"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.35433070866141736" top="0.39370078740157483" bottom="0.4891304347826087" header="0.51181102362204722" footer="0.31496062992125984"/>
